--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>119722577</v>
       </c>
       <c r="B14" t="n">
-        <v>57953</v>
+        <v>57963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>121264558</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>121264558</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>121264558</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>121264558</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2138,7 +2138,7 @@
         <v>121264558</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119722577</v>
+        <v>121591525</v>
       </c>
       <c r="B14" t="n">
-        <v>57963</v>
+        <v>58000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,16 +2057,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Krutebo, Ög</t>
@@ -2079,7 +2077,7 @@
         <v>6415938</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,12 +2101,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2123,12 +2121,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Alfred Olofsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Dennis Jonason</t>
+          <t>Anders Esplund, Enviro Planning</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2253,6 +2251,120 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121591524</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58033</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Krutebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>534594</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6415997</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tidersrum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alfred Olofsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Esplund, Enviro Planning</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2136,7 +2136,7 @@
         <v>121264558</v>
       </c>
       <c r="B15" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Esplund, Enviro Planning</t>
+          <t>Enviro Planning, Anders Esplund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Esplund, Enviro Planning</t>
+          <t>Enviro Planning, Anders Esplund</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 11833-2024 artfynd.xlsx
+++ b/artfynd/A 11833-2024 artfynd.xlsx
@@ -2126,7 +2126,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Enviro Planning, Anders Esplund</t>
+          <t>Anders Esplund, Enviro Planning</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Enviro Planning, Anders Esplund</t>
+          <t>Anders Esplund, Enviro Planning</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
